--- a/prices.xlsx
+++ b/prices.xlsx
@@ -725,7 +725,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -1231,7 +1231,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>88</v>
       </c>
@@ -1315,11 +1315,20 @@
       <c r="B51" t="s">
         <v>103</v>
       </c>
-      <c r="D51" s="4"/>
+      <c r="D51" s="4">
+        <v>4900</v>
+      </c>
       <c r="F51" t="s">
         <v>104</v>
       </c>
     </row>
+    <row r="52" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D52">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="53" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="4:4" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/prices.xlsx
+++ b/prices.xlsx
@@ -109,10 +109,13 @@
     <t>waste-basket-2490</t>
   </si>
   <si>
+    <t>100×100x60cm</t>
+  </si>
+  <si>
     <t>carved-flower-box-lj03</t>
   </si>
   <si>
-    <t>Faragott virágláda (LJ03)</t>
+    <t>100×100x60 cm</t>
   </si>
   <si>
     <t>flower-box-lj01</t>
@@ -121,13 +124,10 @@
     <t>Virágláda (LJ01)</t>
   </si>
   <si>
-    <t>60 × 60 × 60 cm</t>
-  </si>
-  <si>
-    <t>80 × 80 × 60 cm</t>
-  </si>
-  <si>
-    <t>100 × 100 × 60 cm</t>
+    <t>60×60×60cm</t>
+  </si>
+  <si>
+    <t>80×80×60cm</t>
   </si>
   <si>
     <t>water-wheel-well</t>
@@ -905,7 +905,7 @@
         <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D15" s="4">
         <v>2490</v>
@@ -913,10 +913,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D16" s="4">
         <v>1800</v>
@@ -924,13 +924,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" s="4">
         <v>800</v>
@@ -938,13 +938,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D18" s="4">
         <v>990</v>
@@ -952,13 +952,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D19" s="4">
         <v>1200</v>
@@ -1316,17 +1316,13 @@
         <v>103</v>
       </c>
       <c r="D51" s="4">
-        <v>4900</v>
+        <v>60000</v>
       </c>
       <c r="F51" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="52" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D52">
-        <v>60000</v>
-      </c>
-    </row>
+    <row r="52" spans="4:4" x14ac:dyDescent="0.25"/>
     <row r="53" spans="4:4" x14ac:dyDescent="0.25"/>
     <row r="54" spans="4:4" x14ac:dyDescent="0.25"/>
   </sheetData>

--- a/prices.xlsx
+++ b/prices.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="105">
   <si>
     <t>Azonosító (ne szerkeszd)</t>
   </si>
@@ -725,7 +725,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -952,79 +952,76 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D19" s="4">
-        <v>1200</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D20" s="4">
-        <v>11200</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B21" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D21" s="4">
-        <v>2280</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D22" s="4">
-        <v>8850</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B23" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D23" s="4">
-        <v>3500</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B24" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D24" s="4">
-        <v>5700</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B25" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D25" s="4">
         <v>42000</v>
@@ -1032,68 +1029,68 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B26" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D26" s="4">
-        <v>42000</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B27" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D27" s="4">
-        <v>28000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B28" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D28" s="4">
-        <v>21000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+        <v>350</v>
+      </c>
+      <c r="E28" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D29" s="4">
-        <v>350</v>
-      </c>
-      <c r="E29" t="s">
-        <v>59</v>
+        <v>3106</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B30" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D30" s="4">
-        <v>3106</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B31" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D31" s="4">
         <v>3750</v>
@@ -1101,10 +1098,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B32" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D32" s="4">
         <v>3750</v>
@@ -1112,142 +1109,142 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B33" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D33" s="4">
-        <v>3750</v>
+        <v>300</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B34" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D34" s="4">
-        <v>300</v>
+        <v>376</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B35" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D35" s="4">
-        <v>376</v>
+        <v>750</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B36" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D36" s="4">
-        <v>750</v>
+        <v>976</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B37" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D37" s="4">
-        <v>976</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B38" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D38" s="4">
-        <v>3000</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B39" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D39" s="4">
-        <v>8400</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B40" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D40" s="4">
-        <v>5250</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D41" s="4">
-        <v>2500</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B42" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D42" s="4">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B43" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D43" s="4">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B44" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D44" s="4">
-        <v>16500</v>
+        <v>17500</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B45" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D45" s="4">
         <v>17500</v>
@@ -1255,76 +1252,65 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B46" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D46" s="4">
-        <v>17500</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B47" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D47" s="4">
-        <v>28000</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B48" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D48" s="4">
-        <v>3750</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B49" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D49" s="4">
-        <v>21000</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B50" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D50" s="4">
-        <v>4800</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B51" t="s">
-        <v>103</v>
-      </c>
-      <c r="D51" s="4">
         <v>60000</v>
       </c>
-      <c r="F51" t="s">
+      <c r="F50" t="s">
         <v>104</v>
       </c>
     </row>
+    <row r="51" spans="4:4" x14ac:dyDescent="0.25"/>
     <row r="52" spans="4:4" x14ac:dyDescent="0.25"/>
     <row r="53" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="4:4" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/prices.xlsx
+++ b/prices.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="104">
   <si>
     <t>Azonosító (ne szerkeszd)</t>
   </si>
@@ -125,9 +125,6 @@
   </si>
   <si>
     <t>60×60×60cm</t>
-  </si>
-  <si>
-    <t>80×80×60cm</t>
   </si>
   <si>
     <t>water-wheel-well</t>
@@ -725,7 +722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -938,79 +935,76 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D18" s="4">
-        <v>990</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D19" s="4">
-        <v>11200</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D20" s="4">
-        <v>2280</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D21" s="4">
-        <v>8850</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D22" s="4">
-        <v>3500</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D23" s="4">
-        <v>5700</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D24" s="4">
         <v>42000</v>
@@ -1018,68 +1012,68 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D25" s="4">
-        <v>42000</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B26" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D26" s="4">
-        <v>28000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D27" s="4">
-        <v>21000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+        <v>350</v>
+      </c>
+      <c r="E27" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D28" s="4">
-        <v>350</v>
-      </c>
-      <c r="E28" t="s">
-        <v>59</v>
+        <v>3106</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D29" s="4">
-        <v>3106</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B30" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D30" s="4">
         <v>3750</v>
@@ -1087,10 +1081,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B31" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D31" s="4">
         <v>3750</v>
@@ -1098,142 +1092,142 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B32" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D32" s="4">
-        <v>3750</v>
+        <v>300</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B33" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D33" s="4">
-        <v>300</v>
+        <v>376</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D34" s="4">
-        <v>376</v>
+        <v>750</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B35" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D35" s="4">
-        <v>750</v>
+        <v>976</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B36" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D36" s="4">
-        <v>976</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B37" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D37" s="4">
-        <v>3000</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B38" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D38" s="4">
-        <v>8400</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B39" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D39" s="4">
-        <v>5250</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B40" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D40" s="4">
-        <v>2500</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B41" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D41" s="4">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B42" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D42" s="4">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B43" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D43" s="4">
-        <v>16500</v>
+        <v>17500</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B44" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D44" s="4">
         <v>17500</v>
@@ -1241,76 +1235,65 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B45" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D45" s="4">
-        <v>17500</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B46" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D46" s="4">
-        <v>28000</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B47" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D47" s="4">
-        <v>3750</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B48" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D48" s="4">
-        <v>21000</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B49" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D49" s="4">
-        <v>4800</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B50" t="s">
+        <v>60000</v>
+      </c>
+      <c r="F49" t="s">
         <v>103</v>
       </c>
-      <c r="D50" s="4">
-        <v>60000</v>
-      </c>
-      <c r="F50" t="s">
-        <v>104</v>
-      </c>
-    </row>
+    </row>
+    <row r="50" spans="4:4" x14ac:dyDescent="0.25"/>
     <row r="51" spans="4:4" x14ac:dyDescent="0.25"/>
     <row r="52" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="4:4" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/prices.xlsx
+++ b/prices.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="106">
   <si>
     <t>Azonosító (ne szerkeszd)</t>
   </si>
@@ -181,6 +181,15 @@
     <t>Nyolcszögletű pavilon (PAC08)</t>
   </si>
   <si>
+    <t>solid-wood-bell</t>
+  </si>
+  <si>
+    <t>Tömörfa harangláb</t>
+  </si>
+  <si>
+    <t>Please request a quote!</t>
+  </si>
+  <si>
     <t>solid-wood-fence</t>
   </si>
   <si>
@@ -214,6 +223,12 @@
     <t>Mérleghinta (LP01)</t>
   </si>
   <si>
+    <t>swing-frame-sw04</t>
+  </si>
+  <si>
+    <t>Mérleghinta (SW04)</t>
+  </si>
+  <si>
     <t>swing</t>
   </si>
   <si>
@@ -314,15 +329,6 @@
   </si>
   <si>
     <t>Rusztikus tömörfa hinta tetővel</t>
-  </si>
-  <si>
-    <t>solid-wood-bell</t>
-  </si>
-  <si>
-    <t>Tömörfa harangláb</t>
-  </si>
-  <si>
-    <t>Please request a quote!</t>
   </si>
 </sst>
 </file>
@@ -722,7 +728,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -1032,21 +1038,21 @@
         <v>21000</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>56</v>
       </c>
       <c r="B27" t="s">
         <v>57</v>
       </c>
-      <c r="D27" s="4">
-        <v>350</v>
-      </c>
-      <c r="E27" t="s">
+      <c r="D27">
+        <v>60000</v>
+      </c>
+      <c r="F27" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>59</v>
       </c>
@@ -1054,26 +1060,29 @@
         <v>60</v>
       </c>
       <c r="D28" s="4">
-        <v>3106</v>
+        <v>350</v>
+      </c>
+      <c r="E28" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B29" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D29" s="4">
-        <v>3750</v>
+        <v>3106</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D30" s="4">
         <v>3750</v>
@@ -1081,10 +1090,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B31" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D31" s="4">
         <v>3750</v>
@@ -1092,210 +1101,215 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B32" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D32" s="4">
-        <v>300</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>69</v>
+      <c r="A33" t="s">
+        <v>70</v>
       </c>
       <c r="B33" t="s">
-        <v>70</v>
-      </c>
-      <c r="D33" s="4">
-        <v>376</v>
+        <v>71</v>
+      </c>
+      <c r="D33">
+        <v>2900</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D34" s="4">
-        <v>750</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B35" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D35" s="4">
-        <v>976</v>
+        <v>376</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B36" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D36" s="4">
-        <v>3000</v>
+        <v>750</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B37" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D37" s="4">
-        <v>8400</v>
+        <v>976</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B38" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D38" s="4">
-        <v>5250</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B39" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D39" s="4">
-        <v>2500</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B40" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D40" s="4">
-        <v>1050</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B41" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D41" s="4">
-        <v>2100</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B42" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D42" s="4">
-        <v>16500</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B43" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D43" s="4">
-        <v>17500</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B44" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D44" s="4">
-        <v>17500</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B45" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D45" s="4">
-        <v>28000</v>
+        <v>17500</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B46" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D46" s="4">
-        <v>3750</v>
+        <v>17500</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B47" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D47" s="4">
-        <v>21000</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B48" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D48" s="4">
+        <v>3750</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B49" t="s">
+        <v>103</v>
+      </c>
+      <c r="D49" s="4">
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B50" t="s">
+        <v>105</v>
+      </c>
+      <c r="D50" s="4">
         <v>4800</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B49" t="s">
-        <v>102</v>
-      </c>
-      <c r="D49" s="4">
-        <v>60000</v>
-      </c>
-      <c r="F49" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="50" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="51" spans="4:4" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="4:4" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/prices.xlsx
+++ b/prices.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="110">
   <si>
     <t>Azonosító (ne szerkeszd)</t>
   </si>
@@ -34,157 +34,169 @@
     <t>round-bench</t>
   </si>
   <si>
-    <t>Kerek pad (IC06)</t>
+    <t>Kerek pad (GPBS01)</t>
   </si>
   <si>
     <t>bench-bl01</t>
   </si>
   <si>
-    <t>Pad (BL01)</t>
+    <t>Pad (GPBS02)</t>
   </si>
   <si>
     <t>bench-ic01</t>
   </si>
   <si>
-    <t>Pad (IC01)</t>
+    <t>Pad (GPBS03)</t>
   </si>
   <si>
     <t>bench-mi01</t>
   </si>
   <si>
-    <t>Pad (MI01)</t>
+    <t>Pad (GPBS05)</t>
   </si>
   <si>
     <t>bench-st01</t>
   </si>
   <si>
-    <t>Pad (ST01)</t>
+    <t>Pad (GPBS04)</t>
   </si>
   <si>
     <t>bench-mi02</t>
   </si>
   <si>
-    <t>Pad (MI02)</t>
+    <t>Pad (GPBS06)</t>
   </si>
   <si>
     <t>bench-ic02</t>
   </si>
   <si>
-    <t>Pad (IC02)</t>
+    <t>Pad (GPBS07)</t>
   </si>
   <si>
     <t>bench-planter</t>
   </si>
   <si>
-    <t>Pad virágládával</t>
+    <t>Pad virágládával (GPBS08)</t>
   </si>
   <si>
     <t>bench-bike-rack</t>
   </si>
   <si>
-    <t>Pad kerékpártartóval</t>
+    <t>Pad kerékpártartóval (GPBS09)</t>
   </si>
   <si>
     <t>bench-carved</t>
   </si>
   <si>
-    <t>Pad</t>
+    <t>Pad (GPBS10)</t>
   </si>
   <si>
     <t>waste-basket-ib01</t>
   </si>
   <si>
-    <t>Szemetes (IB01)</t>
+    <t>Szemetes (GPWB01)</t>
   </si>
   <si>
     <t>waste-basket-1880</t>
   </si>
   <si>
-    <t>Szemetes</t>
+    <t>Szemetes (GPWB02)</t>
   </si>
   <si>
     <t>waste-basket-1400</t>
   </si>
   <si>
+    <t>Szemetes (GPWB03)</t>
+  </si>
+  <si>
     <t>waste-basket-2490</t>
   </si>
   <si>
-    <t>100×100x60cm</t>
+    <t>100×100x60cm (GPWB04)</t>
   </si>
   <si>
     <t>carved-flower-box-lj03</t>
   </si>
   <si>
-    <t>100×100x60 cm</t>
+    <t>100×100x60 cm (GPPB01)</t>
   </si>
   <si>
     <t>flower-box-lj01</t>
   </si>
   <si>
-    <t>Virágláda (LJ01)</t>
-  </si>
-  <si>
-    <t>60×60×60cm</t>
+    <t>Virágláda (GPPB02)</t>
+  </si>
+  <si>
+    <t>60×60×60 cm</t>
+  </si>
+  <si>
+    <t>80x80x60 cm</t>
+  </si>
+  <si>
+    <t>Virágláda(GPPB02)</t>
+  </si>
+  <si>
+    <t>100x100x60 cm</t>
   </si>
   <si>
     <t>water-wheel-well</t>
   </si>
   <si>
-    <t>Kerekeskút (KK01)</t>
+    <t>Kerekeskút (GPPB03)</t>
   </si>
   <si>
     <t>garden-daybed</t>
   </si>
   <si>
-    <t>Kerti napozóágy (KK01)</t>
+    <t>Kerti napozóágy (GPTS01)</t>
   </si>
   <si>
     <t>round-bench-table</t>
   </si>
   <si>
-    <t>Kerek pad és asztal (IC60)</t>
+    <t>Kerek pad és asztal (GPTS02)</t>
   </si>
   <si>
     <t>table-icm01</t>
   </si>
   <si>
-    <t>Asztal (ICM01)</t>
+    <t>Asztal (GPTS03)</t>
   </si>
   <si>
     <t>chess-table</t>
   </si>
   <si>
-    <t>Sakkasztal két paddal (SA01)</t>
+    <t>Sakkasztal két paddal (GPTS04)</t>
   </si>
   <si>
     <t>bus-stop-bm02</t>
   </si>
   <si>
-    <t>Buszmegálló (BM02)</t>
+    <t>Buszmegálló (GPSS01)</t>
   </si>
   <si>
     <t>bus-stop-bm01</t>
   </si>
   <si>
-    <t>Buszmegálló (BM01)</t>
+    <t>Buszmegálló (GPSS02)</t>
   </si>
   <si>
     <t>szekely-gate</t>
   </si>
   <si>
-    <t>Székelykapu (BM01)</t>
+    <t>Székelykapu (GPSS03)</t>
   </si>
   <si>
     <t>octagonal-pavilion</t>
   </si>
   <si>
-    <t>Nyolcszögletű pavilon (PAC08)</t>
+    <t>Nyolcszögletű pavilon (GPSS04)</t>
   </si>
   <si>
     <t>solid-wood-bell</t>
   </si>
   <si>
-    <t>Tömörfa harangláb</t>
+    <t>Tömörfa harangláb (GPSS05)</t>
   </si>
   <si>
     <t>Please request a quote!</t>
@@ -193,7 +205,7 @@
     <t>solid-wood-fence</t>
   </si>
   <si>
-    <t>Tömörfa kerítés</t>
+    <t>Tömörfa kerítés (GPFS01)</t>
   </si>
   <si>
     <t>lei/m</t>
@@ -202,133 +214,133 @@
     <t>information-board</t>
   </si>
   <si>
-    <t>Információs tábla (HT01)</t>
+    <t>Információs tábla (GPFS02)</t>
   </si>
   <si>
     <t>bike-rack-bt01</t>
   </si>
   <si>
-    <t>Kerékpártartó (BT01)</t>
+    <t>Kerékpártartó (GPFS03)</t>
   </si>
   <si>
     <t>swing-frame-lp02</t>
   </si>
   <si>
-    <t>Mérleghinta (LP02)</t>
+    <t>Mérleghinta (GPPS02)</t>
   </si>
   <si>
     <t>swing-frame-lp01</t>
   </si>
   <si>
-    <t>Mérleghinta (LP01)</t>
+    <t>Mérleghinta (GPPS01)</t>
   </si>
   <si>
     <t>swing-frame-sw04</t>
   </si>
   <si>
-    <t>Mérleghinta (SW04)</t>
+    <t>Mérleghinta (GPPS03)</t>
   </si>
   <si>
     <t>swing</t>
   </si>
   <si>
-    <t>Hinta</t>
+    <t>Hinta (GPPS04)</t>
   </si>
   <si>
     <t>childrens-swing</t>
   </si>
   <si>
-    <t>Gyermekhinta</t>
+    <t>Gyermekhinta (GPPS05)</t>
   </si>
   <si>
     <t>large-swing</t>
   </si>
   <si>
-    <t>Nagy hinta</t>
+    <t>Nagy hinta (GPPS07)</t>
   </si>
   <si>
     <t>hexagonal-sandpit</t>
   </si>
   <si>
-    <t>Hatszögletű homokozó</t>
+    <t>Hatszögletű homokozó (GPPS06)</t>
   </si>
   <si>
     <t>balance-beam</t>
   </si>
   <si>
-    <t>Egyensúlyozó kígyó (EKO1)</t>
+    <t>Egyensúlyozó kígyó (GPPS08)</t>
   </si>
   <si>
     <t>hexagonal-climbing</t>
   </si>
   <si>
-    <t>Hatszögletű mászóka (MFO1)</t>
+    <t>Hatszögletű mászóka (GPPS09)</t>
   </si>
   <si>
     <t>small-boat</t>
   </si>
   <si>
-    <t>Kishajó (BOATOT)</t>
+    <t>Kishajó (GPPS10)</t>
   </si>
   <si>
     <t>airplane-curved</t>
   </si>
   <si>
-    <t>Rugós repülő (APO1ARC)</t>
+    <t>Rugós repülő (GPPS11)</t>
   </si>
   <si>
     <t>sensory-maze</t>
   </si>
   <si>
-    <t>Szenzomotoros fejlesztő labirintusjáték (EL01)</t>
+    <t>Szenzomotoros fejlesztő labirintusjáték (GPPS12)</t>
   </si>
   <si>
     <t>airplane-ap01</t>
   </si>
   <si>
-    <t>Repülő (AP01)</t>
+    <t>Repülő (GPPS13)</t>
   </si>
   <si>
     <t>mini-playground</t>
   </si>
   <si>
-    <t>Mini vár típusú játszókomplexum (MINI01)</t>
+    <t>Mini vár típusú játszókomplexum (GPLP01)</t>
   </si>
   <si>
     <t>two-seat-swing-tw02</t>
   </si>
   <si>
-    <t>Dupla tömörfa hintaállvány torony típusú csúszdával (TW02)</t>
+    <t>Dupla tömörfa hintaállvány torony típusú csúszdával (GPLP02)</t>
   </si>
   <si>
     <t>two-seat-swing-tw03</t>
   </si>
   <si>
-    <t>Dupla tömörfa hintaállvány csúszdával (TW03)</t>
+    <t>Dupla tömörfa hintaállvány csúszdával (GPLP03)</t>
   </si>
   <si>
     <t>steamboat-karibi</t>
   </si>
   <si>
-    <t>Karibi hajó (KARIBI)</t>
+    <t>Karibi hajó (GPLP04)</t>
   </si>
   <si>
     <t>rustic-two-seat-swing</t>
   </si>
   <si>
-    <t>Rusztikus dupla tömörfa hinta</t>
+    <t>Rusztikus dupla tömörfa hinta (GPLP05)</t>
   </si>
   <si>
     <t>carousel</t>
   </si>
   <si>
-    <t>Körhinta</t>
+    <t>Körhinta (GPLP06)</t>
   </si>
   <si>
     <t>rustic-swing-roof</t>
   </si>
   <si>
-    <t>Rusztikus tömörfa hinta tetővel</t>
+    <t>Rusztikus tömörfa hinta tetővel (GPLP07)</t>
   </si>
 </sst>
 </file>
@@ -728,7 +740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
@@ -897,7 +909,7 @@
         <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D14" s="4">
         <v>1400</v>
@@ -905,10 +917,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D15" s="4">
         <v>2490</v>
@@ -916,10 +928,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D16" s="4">
         <v>1800</v>
@@ -927,38 +939,44 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" s="4">
         <v>800</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>38</v>
+      <c r="A18" t="s">
+        <v>36</v>
       </c>
       <c r="B18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="4">
-        <v>11200</v>
+      <c r="D18">
+        <v>990</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
+      <c r="A19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" t="s">
         <v>40</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="4">
-        <v>2280</v>
+      <c r="D19">
+        <v>1200</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -969,7 +987,7 @@
         <v>43</v>
       </c>
       <c r="D20" s="4">
-        <v>8850</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -980,7 +998,7 @@
         <v>45</v>
       </c>
       <c r="D21" s="4">
-        <v>3500</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -991,7 +1009,7 @@
         <v>47</v>
       </c>
       <c r="D22" s="4">
-        <v>5700</v>
+        <v>8850</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -1002,7 +1020,7 @@
         <v>49</v>
       </c>
       <c r="D23" s="4">
-        <v>42000</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -1013,7 +1031,7 @@
         <v>51</v>
       </c>
       <c r="D24" s="4">
-        <v>42000</v>
+        <v>5700</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1024,7 +1042,7 @@
         <v>53</v>
       </c>
       <c r="D25" s="4">
-        <v>28000</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -1035,57 +1053,57 @@
         <v>55</v>
       </c>
       <c r="D26" s="4">
-        <v>21000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
+        <v>42000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
         <v>56</v>
       </c>
       <c r="B27" t="s">
         <v>57</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="4">
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28" s="4">
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" t="s">
+        <v>61</v>
+      </c>
+      <c r="D29">
         <v>60000</v>
       </c>
-      <c r="F27" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B28" t="s">
-        <v>60</v>
-      </c>
-      <c r="D28" s="4">
+      <c r="F29" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B30" t="s">
+        <v>64</v>
+      </c>
+      <c r="D30" s="4">
         <v>350</v>
       </c>
-      <c r="E28" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B29" t="s">
-        <v>63</v>
-      </c>
-      <c r="D29" s="4">
-        <v>3106</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B30" t="s">
+      <c r="E30" t="s">
         <v>65</v>
-      </c>
-      <c r="D30" s="4">
-        <v>3750</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -1096,7 +1114,7 @@
         <v>67</v>
       </c>
       <c r="D31" s="4">
-        <v>3750</v>
+        <v>3106</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -1111,14 +1129,14 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="A33" s="3" t="s">
         <v>70</v>
       </c>
       <c r="B33" t="s">
         <v>71</v>
       </c>
-      <c r="D33">
-        <v>2900</v>
+      <c r="D33" s="4">
+        <v>3750</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -1129,18 +1147,18 @@
         <v>73</v>
       </c>
       <c r="D34" s="4">
-        <v>300</v>
+        <v>3750</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
+      <c r="A35" t="s">
         <v>74</v>
       </c>
       <c r="B35" t="s">
         <v>75</v>
       </c>
-      <c r="D35" s="4">
-        <v>376</v>
+      <c r="D35">
+        <v>2900</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -1151,7 +1169,7 @@
         <v>77</v>
       </c>
       <c r="D36" s="4">
-        <v>750</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1162,7 +1180,7 @@
         <v>79</v>
       </c>
       <c r="D37" s="4">
-        <v>976</v>
+        <v>376</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1173,7 +1191,7 @@
         <v>81</v>
       </c>
       <c r="D38" s="4">
-        <v>3000</v>
+        <v>750</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -1184,7 +1202,7 @@
         <v>83</v>
       </c>
       <c r="D39" s="4">
-        <v>8400</v>
+        <v>976</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -1195,7 +1213,7 @@
         <v>85</v>
       </c>
       <c r="D40" s="4">
-        <v>5250</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -1206,7 +1224,7 @@
         <v>87</v>
       </c>
       <c r="D41" s="4">
-        <v>2500</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1217,7 +1235,7 @@
         <v>89</v>
       </c>
       <c r="D42" s="4">
-        <v>1050</v>
+        <v>5250</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -1228,7 +1246,7 @@
         <v>91</v>
       </c>
       <c r="D43" s="4">
-        <v>2100</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -1239,7 +1257,7 @@
         <v>93</v>
       </c>
       <c r="D44" s="4">
-        <v>16500</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -1250,7 +1268,7 @@
         <v>95</v>
       </c>
       <c r="D45" s="4">
-        <v>17500</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -1261,7 +1279,7 @@
         <v>97</v>
       </c>
       <c r="D46" s="4">
-        <v>17500</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1272,7 +1290,7 @@
         <v>99</v>
       </c>
       <c r="D47" s="4">
-        <v>28000</v>
+        <v>17500</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -1283,7 +1301,7 @@
         <v>101</v>
       </c>
       <c r="D48" s="4">
-        <v>3750</v>
+        <v>17500</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -1294,7 +1312,7 @@
         <v>103</v>
       </c>
       <c r="D49" s="4">
-        <v>21000</v>
+        <v>28000</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1305,11 +1323,33 @@
         <v>105</v>
       </c>
       <c r="D50" s="4">
+        <v>3750</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B51" t="s">
+        <v>107</v>
+      </c>
+      <c r="D51" s="4">
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B52" t="s">
+        <v>109</v>
+      </c>
+      <c r="D52" s="4">
         <v>4800</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/prices.xlsx
+++ b/prices.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="110">
   <si>
     <t>Azonosító (ne szerkeszd)</t>
   </si>
@@ -145,6 +145,9 @@
     <t>Kerekeskút (GPPB03)</t>
   </si>
   <si>
+    <t>Please request a price!</t>
+  </si>
+  <si>
     <t>garden-daybed</t>
   </si>
   <si>
@@ -197,9 +200,6 @@
   </si>
   <si>
     <t>Tömörfa harangláb (GPSS05)</t>
-  </si>
-  <si>
-    <t>Please request a quote!</t>
   </si>
   <si>
     <t>solid-wood-fence</t>
@@ -744,7 +744,7 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="40" customWidth="1"/>
+    <col min="2" max="2" width="43" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
@@ -979,23 +979,24 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>42</v>
       </c>
       <c r="B20" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="4">
-        <v>11200</v>
+      <c r="D20" s="4"/>
+      <c r="F20" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D21" s="4">
         <v>2280</v>
@@ -1003,10 +1004,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D22" s="4">
         <v>8850</v>
@@ -1014,10 +1015,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D23" s="4">
         <v>3500</v>
@@ -1025,10 +1026,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D24" s="4">
         <v>5700</v>
@@ -1036,10 +1037,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B25" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D25" s="4">
         <v>42000</v>
@@ -1047,32 +1048,33 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D26" s="4">
         <v>42000</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
-      </c>
-      <c r="D27" s="4">
-        <v>28000</v>
+        <v>58</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="F27" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B28" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D28" s="4">
         <v>21000</v>
@@ -1080,16 +1082,13 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B29" t="s">
-        <v>61</v>
-      </c>
-      <c r="D29">
-        <v>60000</v>
+        <v>62</v>
       </c>
       <c r="F29" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1350,6 +1349,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>